--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00913-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00913-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41D6ADEA-5207-46C4-A671-413DA59BC107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC977B44-069B-49C8-9C0E-44CDAD0D7B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D4FB5883-2CA0-4F01-842E-32EE6E0C3793}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CBB2014E-7805-40FC-B13B-8934978576D4}"/>
   </bookViews>
   <sheets>
     <sheet name="00913-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1513,20 +1513,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D23C99-C2E1-46D3-9F3A-5ECB44741C9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E389F243-84B4-404C-A98A-86F516681705}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1680,7 +1680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1760,7 +1760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
         <v>42</v>
       </c>
